--- a/data/raw/promotions/promociones_2026-43.xlsx
+++ b/data/raw/promotions/promociones_2026-43.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MA-MUE-0006</t>
+          <t>SKU-AIRCON-PE-00363</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MA-COC-0007</t>
+          <t>SKU-AUT-EC-00033</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MA-JAR-0008</t>
+          <t>SKU-ART-BO-00696</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -547,7 +547,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MA-ANI-0009</t>
+          <t>SKU-AIRCON-CL-00375</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,12 +568,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MA-TOY-0010</t>
+          <t>SKU-AGRINDAND-BO-00565</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CANAL_ECOMMERCE</t>
+          <t>BO_E-commerce Propio</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -589,12 +589,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MA-TEL-0011</t>
+          <t>SKU-AIRCON-BO-00366</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CANAL_MARKETPLACE</t>
+          <t>BO_Marketplace Propietario</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -610,7 +610,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MA-PAP-0012</t>
+          <t>SKU-BOOTEC-CO-00599</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MA-MOD-0013</t>
+          <t>SKU-CDSDVDMUS-CO-00966</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -652,7 +652,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MA-LIB-0014</t>
+          <t>SKU-AIRCON-PE-00370</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MA-AUT-0015</t>
+          <t>SKU-AUT-EC-00041</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
